--- a/docs/bulk-templates/users_sample.xlsx
+++ b/docs/bulk-templates/users_sample.xlsx
@@ -446,7 +446,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G7"/>
+  <dimension ref="A1:F7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -454,8 +454,7 @@
     <col width="29" customWidth="1" min="3" max="3"/>
     <col width="14" customWidth="1" min="4" max="4"/>
     <col width="12" customWidth="1" min="5" max="5"/>
-    <col width="13" customWidth="1" min="6" max="6"/>
-    <col width="12" customWidth="1" min="7" max="7"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -486,11 +485,6 @@
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
-          <t>password</t>
-        </is>
-      </c>
-      <c r="G1" s="1" t="inlineStr">
-        <is>
           <t>vendor_uid</t>
         </is>
       </c>
@@ -521,8 +515,7 @@
           <t>9811110001</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
-      <c r="G2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>VND-001</t>
         </is>
@@ -556,11 +549,6 @@
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>Welcome@123</t>
-        </is>
-      </c>
-      <c r="G3" s="2" t="inlineStr">
-        <is>
           <t>VND-001</t>
         </is>
       </c>
@@ -591,8 +579,7 @@
           <t>9811110003</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
-      <c r="G4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>VND-001</t>
         </is>
@@ -624,8 +611,7 @@
           <t>9811110004</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>VND-002</t>
         </is>
@@ -657,8 +643,7 @@
           <t>9811110005</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
-      <c r="G6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>VND-002</t>
         </is>
@@ -691,7 +676,6 @@
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr"/>
-      <c r="G7" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
@@ -709,7 +693,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C8"/>
+  <dimension ref="A1:C7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -822,7 +806,7 @@
     <row r="7">
       <c r="A7" s="4" t="inlineStr">
         <is>
-          <t>password</t>
+          <t>vendor_uid</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -831,23 +815,6 @@
         </is>
       </c>
       <c r="C7" t="inlineStr">
-        <is>
-          <t>Initial password (defaults to password123 if blank).</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" s="4" t="inlineStr">
-        <is>
-          <t>vendor_uid</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>Optional</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
         <is>
           <t>Required for employee/vendor roles. Must exist, e.g. VND-001.</t>
         </is>
